--- a/public/documents/pieces-reponse-1/R1-inventaires-comparatif.xlsx
+++ b/public/documents/pieces-reponse-1/R1-inventaires-comparatif.xlsx
@@ -13,6 +13,8 @@
     <sheet name="Cloture 2024-03-31" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cloture 2025-03-31" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Recapitulatif" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recapitulatifs dates" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Corrections et reserves" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,6 +136,16 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10382,4 +10394,377 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Cloture</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Intitule porte sur la page recapitulative</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Boissons sans alcool</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Vins et alcools</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Total boissons</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Autres postes inventories</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Total imprime sur la page</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>INVENTAIRE H.T. DEMI LUNE 31/03/2023</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>727.7</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>3050.29</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>3777.99</v>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>ALIMENTAIRE (frais, surgeles, epicerie) : 1734.15 ; CREMERIE : 158.85 ; VIANDE-CHARCUTERIE : 255.63 ; PRODUITS D'ENTRETIEN ET DIVERS : 1103.99</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>7030.61</v>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Inventaire_Demi_Lune_2023-03-31.pdf, p. 1 (tableau dactylographie, date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>INVENTAIRE H.T. AU 31 MARS 2024</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>870.59</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>3937.07</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>4807.66</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Produits d'entretien et Divers : 1000.30 ; Alimentation : 4065.17</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>9873.07</v>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Inventaire_Demi_Lune_2024-03-31.pdf, p. 1 (page dactylographiee, datee) ; report manuscrit des memes totaux en p. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>INVENTAIRE HT 31/03/2025</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>765.74</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>3768.51</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>4534.25</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ALIMENTATION (frais, surgeles, epicerie) : 3654.92 ; DIVERS NON COMESTIBLES : 1585.00</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>9774.17</v>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Inventaire_Demi_Lune_2025-03-31.pdf, p. 1 (page dactylographiee, datee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Rapprochement avec la variation de stock boissons retenue par le service (compte 310200), sous la convention comptable variation = stock initial moins stock final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Stock initial</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Stock final</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SI - SF</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Variation retenue (310200)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Ecart</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>stock au 31/03/2022 non repris</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3777.99</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="n">
+        <v>-800.83</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>3777.99</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>4807.66</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>-1029.67</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>-1029.67</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>4807.66</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>4534.25</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>273.41</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-273.41</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>546.8200000000001</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Objet</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Incidence (EUR HT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Erreurs de frappe rectifiees (cloture 31/03/2023)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Clan Campbell 70cl : 17.56 saisi au lieu de 12.56 ; Creme de Mure 100cl : 8.22 saisi au lieu de 8.27 ; Creme de Cerise 100cl : 16.78 saisi au lieu de 15.76</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>-5.97</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Total alcools et vins au 31/03/2023, apres rectification</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3 056,26 EUR transcrits, 3 050,29 EUR portes sur l'etat d'origine (page 11 du PDF 2023, reproduite par le service p. 33 de sa reponse). C'est l'etat d'origine qui fait foi.</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>3050.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Colonne de fiabilite de la transcription</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>27 lignes sur 273 sont marquees « a verifier » dans les CSV publies (1 929,34 EUR), dont trois lignes de reconciliation au 31/03/2025 qui ne designent aucun produit (413,00 EUR). Ces reserves portent sur la TRANSCRIPTION, pas sur les etats d'origine, dont les totaux dates figurent dans la feuille precedente.</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>1929.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Perimetre du CSV</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Les CSV retiennent les seules boissons : ils excluent les biscuits, le sucre, les pailles et les consommables inscrits sur les memes pages d'inventaire. Leurs totaux ne sont donc pas comparables aux totaux des pages recapitulatives.</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/documents/pieces-reponse-1/R1-inventaires-comparatif.xlsx
+++ b/public/documents/pieces-reponse-1/R1-inventaires-comparatif.xlsx
@@ -65,12 +65,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -127,14 +127,8 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +138,9 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -573,7 +570,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sur les 21 articles reproduits par le service : quantites identiques sur 21 lignes, valeurs identiques au centime sur 18 lignes. Ecart de valeur cumule : +5.97 EUR sur un total de 451.80 EUR.</t>
+          <t>Sur les 21 articles reproduits par le service : quantites identiques sur 21 lignes, valeurs identiques au centime sur 21 lignes. Ecart de valeur cumule : +0.00 EUR sur un total de 451.80 EUR.</t>
         </is>
       </c>
     </row>
@@ -585,7 +582,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Les rares ecarts sont des erreurs de frappe de la retranscription informatique ; l'etat d'origine, joint en PDF, fait foi. Ils ne proviennent d'aucune modification de l'inventaire physique.</t>
+          <t>L'etat d'origine, joint en PDF, fait foi. Les ecarts que presentait la retranscription informatique etaient des erreurs de frappe, rectifiees et recapitulees dans la feuille « Corrections et reserves » ; elles ne provenaient d'aucune modification de l'inventaire physique.</t>
         </is>
       </c>
     </row>
@@ -597,7 +594,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Comparatif p.33 ; Cloture 31-03-2023 ; Cloture 31-03-2024 ; Cloture 31-03-2025 ; Recapitulatif.</t>
+          <t>8 onglets : Notice ; Comparatif p.33 ; Cloture 2023-03-31 ; Cloture 2024-03-31 ; Cloture 2025-03-31 ; Recapitulatif ; Recapitulatifs dates ; Corrections et reserves.</t>
         </is>
       </c>
     </row>
@@ -902,16 +899,16 @@
         <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>17.56</v>
+        <v>12.56</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="J6" s="10" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="J6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="11" t="n">
-        <v>5</v>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1189,16 +1186,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="J13" s="10" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="11" t="n">
-        <v>-0.05</v>
+      <c r="K13" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1271,16 +1268,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="J15" s="10" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>1.02</v>
+      <c r="K15" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1571,26 +1568,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="13" t="n">
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="11" t="n">
         <v>451.8</v>
       </c>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="13" t="n">
-        <v>457.77</v>
-      </c>
-      <c r="J23" s="12" t="inlineStr"/>
-      <c r="K23" s="13" t="n">
-        <v>5.97</v>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="11" t="n">
+        <v>451.8</v>
+      </c>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1604,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1754,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6.42</v>
+        <v>3.44</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -1859,13 +1856,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1938,7 +1935,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Vittel 50cl</t>
+          <t>San Pellegrino 50cl</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1969,12 +1966,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>San Pellegrino 50cl</t>
+          <t>San Pellegrino 100cl</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>50 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1983,13 +1980,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>29.04</v>
+        <v>28.75</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -2000,12 +1997,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>San Pellegrino 100cl</t>
+          <t>Orangina 33cl</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>33 cl</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2014,13 +2011,13 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1.15</v>
+        <v>0.59</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>28.75</v>
+        <v>19.47</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -2031,7 +2028,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Orangina 33cl</t>
+          <t>Fanta 33cl</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2045,13 +2042,13 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.59</v>
+        <v>0.65</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>19.47</v>
+        <v>14.95</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -2062,7 +2059,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Fanta 33cl</t>
+          <t>Schweppes 33cl</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2076,13 +2073,13 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>14.95</v>
+        <v>20.74</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -2093,12 +2090,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Schweppes 33cl</t>
+          <t>Limonade Mortuacienne 1L</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>33 cl</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2107,13 +2104,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.61</v>
+        <v>0.96</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>20.74</v>
+        <v>13.44</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -2124,27 +2121,23 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Limonade Mortuacienne 1L</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>1 l</t>
-        </is>
-      </c>
+          <t>Granini Nectar Ananas</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Boissons sans alcool</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.96</v>
+        <v>3.22</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>13.44</v>
+        <v>28.98</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -2155,7 +2148,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Granini Nectar Ananas</t>
+          <t>Granini Nectar Poire</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
@@ -2165,13 +2158,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>28.98</v>
+        <v>27.28</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -2182,7 +2175,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Granini Nectar Poire</t>
+          <t>Granini Jus Orange</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -2192,13 +2185,13 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2.48</v>
+        <v>3.13</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>27.28</v>
+        <v>18.78</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -2209,7 +2202,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Granini Jus Orange</t>
+          <t>Granini Jus Ananas</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -2219,13 +2212,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>18.78</v>
+        <v>9.42</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -2236,23 +2229,27 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Granini Jus Ananas</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
+          <t>Granini Framboise 25cl</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Boissons sans alcool</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3.14</v>
+        <v>1.31</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>9.42</v>
+        <v>32.75</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -2263,7 +2260,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Granini Framboise 25cl</t>
+          <t>Granini Fraise 25cl</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2277,13 +2274,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>32.75</v>
+        <v>38.08</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -2294,7 +2291,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Granini Fraise 25cl</t>
+          <t>Granini Raisin 25cl</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2308,13 +2305,13 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>38.08</v>
+        <v>20.33</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -2325,7 +2322,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Granini Raisin 25cl</t>
+          <t>Granini Tomate 25cl</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2339,13 +2336,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>20.33</v>
+        <v>16.83</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -2356,12 +2353,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Granini Tomate 25cl</t>
+          <t>Coca-Cola 33cl</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>25 cl</t>
+          <t>33 cl</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2370,13 +2367,13 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>16.83</v>
+        <v>58.88</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -2387,7 +2384,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola 33cl</t>
+          <t>Fuze Tea 33cl</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2401,13 +2398,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>58.88</v>
+        <v>16.9</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -2418,12 +2415,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Fuze Tea 33cl</t>
+          <t>Monin Pêche 100cl</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>33 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2432,13 +2429,13 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.65</v>
+        <v>5.99</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>16.9</v>
+        <v>5.99</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
@@ -2449,7 +2446,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Monin Pêche 100cl</t>
+          <t>Monin Fraise 100cl</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2466,10 +2463,10 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>5.99</v>
+        <v>5.31</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>5.99</v>
+        <v>5.31</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -2480,7 +2477,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Monin Fraise 100cl</t>
+          <t>Monin Châtaigne 100cl</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2494,13 +2491,13 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>5.31</v>
+        <v>16.5</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -2511,7 +2508,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Monin Châtaigne 100cl</t>
+          <t>Monin Framboise 100cl</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2525,13 +2522,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>5.5</v>
+        <v>6.23</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>16.5</v>
+        <v>6.23</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
@@ -2542,7 +2539,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Monin Framboise 100cl</t>
+          <t>Monin Citron 100cl</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2559,10 +2556,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>6.23</v>
+        <v>4.55</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>6.23</v>
+        <v>4.55</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -2573,7 +2570,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Monin Citron 100cl</t>
+          <t>Monin Orange 100cl</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2587,13 +2584,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>4.55</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>4.55</v>
+        <v>9.1</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
@@ -2604,7 +2601,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Monin Orange 100cl</t>
+          <t>Monin Grenadine 100cl</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2618,13 +2615,13 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>4.55</v>
+        <v>4.23</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>9.1</v>
+        <v>4.23</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
@@ -2635,7 +2632,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Monin Grenadine 100cl</t>
+          <t>Monin Menthe 100cl</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2652,10 +2649,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>4.23</v>
+        <v>4.55</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>4.23</v>
+        <v>4.55</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
@@ -2666,27 +2663,23 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Monin Menthe 100cl</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>100 cl</t>
-        </is>
-      </c>
+          <t>Routin Citron Acide</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Boissons sans alcool</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>4.55</v>
+        <v>7.64</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
@@ -2697,10 +2690,14 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Routin Citron Acide</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr"/>
+          <t>Monin Pamplemousse 100cl</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>100 cl</t>
+        </is>
+      </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Boissons sans alcool</t>
@@ -2710,10 +2707,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>3.82</v>
+        <v>5.5</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>7.64</v>
+        <v>11</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
@@ -2724,7 +2721,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Monin Pamplemousse 100cl</t>
+          <t>Monin Curaçao 100cl</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2738,13 +2735,13 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>11</v>
+        <v>5.25</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -2755,38 +2752,38 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Monin Curaçao 100cl</t>
+          <t>Rouget de Lisle Blanche 33cl</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>33 cl</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Boissons sans alcool</t>
+          <t>Alcools et vins</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>5.25</v>
+        <v>73.8</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Blanche 33cl</t>
+          <t>Rouget de Lisle Ambrée 33cl</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2800,13 +2797,13 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>73.8</v>
+        <v>64.8</v>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
@@ -2817,12 +2814,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Ambrée 33cl</t>
+          <t>Fût Affligem 8L</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>33 cl</t>
+          <t>8 l</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2831,13 +2828,13 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.8</v>
+        <v>4.07</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>64.8</v>
+        <v>16.28</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -2848,12 +2845,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Fût Affligem 8L</t>
+          <t>Cidre La Mordue 27cl</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>8 l</t>
+          <t>27 cl</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2862,13 +2859,13 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>4.07</v>
+        <v>1.13</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>16.28</v>
+        <v>36.16</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -2879,12 +2876,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Cidre La Mordue 27cl</t>
+          <t>Cidre Brut 75cl</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>27 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2893,13 +2890,13 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1.13</v>
+        <v>2.54</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>36.16</v>
+        <v>38.1</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
@@ -2910,7 +2907,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Cidre Brut 75cl</t>
+          <t>Cidre Doux 75cl</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2924,13 +2921,13 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>38.1</v>
+        <v>40.46</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
@@ -2941,12 +2938,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Cidre Doux 75cl</t>
+          <t>Pontarlier Anis 100cl</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2955,13 +2952,13 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2.89</v>
+        <v>17.95</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>40.46</v>
+        <v>17.95</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -2972,7 +2969,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Pontarlier Anis 100cl</t>
+          <t>Ricard 100cl</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2989,10 +2986,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>17.95</v>
+        <v>17.56</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>17.95</v>
+        <v>17.56</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -3003,12 +3000,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Ricard 100cl</t>
+          <t>Clan Campbell 70cl</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3020,10 +3017,10 @@
         <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>17.56</v>
+        <v>12.56</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>17.56</v>
+        <v>12.56</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -3034,7 +3031,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Clan Campbell 70cl</t>
+          <t>Jack Daniel's 70cl</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -3051,10 +3048,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>17.56</v>
+        <v>19.26</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>17.56</v>
+        <v>19.26</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -3065,7 +3062,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Jack Daniel's 70cl</t>
+          <t>Marc du Jura 70cl</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3082,10 +3079,10 @@
         <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>19.26</v>
+        <v>18.61</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>19.26</v>
+        <v>18.61</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -3096,12 +3093,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Marc du Jura 70cl</t>
+          <t>Martini 100cl</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3113,10 +3110,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>18.61</v>
+        <v>8.15</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>18.61</v>
+        <v>8.15</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -3127,12 +3124,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Martini 100cl</t>
+          <t>Marc de Bourgogne 70cl</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3141,13 +3138,13 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>8.15</v>
+        <v>25.9</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -3158,12 +3155,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne 70cl</t>
+          <t>Porto 75cl</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3172,13 +3169,13 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>25.9</v>
+        <v>7.71</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0</v>
+        <v>30.84</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -3189,12 +3186,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Porto 75cl</t>
+          <t>Liqueur de Sapin 100cl</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3203,13 +3200,13 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7.71</v>
+        <v>21.16</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>30.84</v>
+        <v>42.32</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -3220,7 +3217,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin 100cl</t>
+          <t>Crème de Mûre 100cl</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -3234,13 +3231,13 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>21.16</v>
+        <v>8.27</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>42.32</v>
+        <v>8.27</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -3251,7 +3248,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Crème de Mûre 100cl</t>
+          <t>Crème de Cassis 100cl</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3265,13 +3262,13 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>8.220000000000001</v>
+        <v>16.78</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -3282,7 +3279,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Crème de Cassis 100cl</t>
+          <t>Crème de Cerise 100cl</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -3299,10 +3296,10 @@
         <v>2</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>16.78</v>
+        <v>15.76</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -3313,12 +3310,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Crème de Cerise 100cl</t>
+          <t>Vodka Poliakov 70cl</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3327,13 +3324,13 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>16.78</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -3344,7 +3341,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Vodka Poliakov 70cl</t>
+          <t>Cognac Park 70cl</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -3361,10 +3358,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>9.029999999999999</v>
+        <v>19.62</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>9.029999999999999</v>
+        <v>19.62</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -3375,7 +3372,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Cognac Park 70cl</t>
+          <t>Absinthe 70cl</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3389,13 +3386,13 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>19.62</v>
+        <v>30.89</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>19.62</v>
+        <v>61.78</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -3406,12 +3403,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Absinthe 70cl</t>
+          <t>Calvados 100cl</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3423,10 +3420,10 @@
         <v>2</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>30.89</v>
+        <v>16.53</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>61.78</v>
+        <v>33.06</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -3437,12 +3434,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Calvados 100cl</t>
+          <t>Mirabelle 70cl</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3451,13 +3448,13 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>16.53</v>
+        <v>20.04</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>33.06</v>
+        <v>20.04</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -3468,7 +3465,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Mirabelle 70cl</t>
+          <t>Eau de Vie Framboise 70cl</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -3485,10 +3482,10 @@
         <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>20.04</v>
+        <v>21.65</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>20.04</v>
+        <v>21.65</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -3499,7 +3496,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise 70cl</t>
+          <t>Soho Litchi 70cl</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3513,13 +3510,13 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.65</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>21.65</v>
+        <v>0</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -3530,7 +3527,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Soho Litchi 70cl</t>
+          <t>Passoa 70cl</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -3544,13 +3541,13 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0</v>
+        <v>18.16</v>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
@@ -3561,7 +3558,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Passoa 70cl</t>
+          <t>Bailey's 70cl</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3575,13 +3572,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>9.08</v>
+        <v>12.99</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>18.16</v>
+        <v>0</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3592,12 +3589,12 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Bailey's 70cl</t>
+          <t>Picon 100cl</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>100 cl</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -3606,13 +3603,13 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>12.99</v>
+        <v>10.43</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0</v>
+        <v>10.43</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
@@ -3623,12 +3620,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Picon 100cl</t>
+          <t>Get 27 70cl</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>100 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3640,10 +3637,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>10.43</v>
+        <v>15.36</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>10.43</v>
+        <v>15.36</v>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
@@ -3654,7 +3651,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Get 27 70cl</t>
+          <t>Get 31 70cl</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -3671,10 +3668,10 @@
         <v>1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>15.36</v>
+        <v>17.26</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>15.36</v>
+        <v>17.26</v>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
@@ -3685,7 +3682,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Get 31 70cl</t>
+          <t>Génépi 70cl</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -3702,10 +3699,10 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>17.26</v>
+        <v>22.66</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>17.26</v>
+        <v>22.66</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -3716,12 +3713,12 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Génépi 70cl</t>
+          <t>Ravelin Blanc 99cl</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>99 cl</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3730,13 +3727,13 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>22.66</v>
+        <v>3.25</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>22.66</v>
+        <v>0</v>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
@@ -3747,12 +3744,12 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Ravelin Blanc 99cl</t>
+          <t>Chardonnay Tradition 75cl</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>99 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3764,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>3.25</v>
+        <v>6.48</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>0</v>
@@ -3778,12 +3775,12 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay Tradition 75cl</t>
+          <t>Bourgogne Aligoté BIB 10L</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>10 l</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3792,13 +3789,13 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>6.48</v>
+        <v>51.24</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>0</v>
+        <v>51.24</v>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
@@ -3809,7 +3806,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté BIB 10L</t>
+          <t>BIB Côtes de Provence Rosé 10L</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -3823,13 +3820,13 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>51.24</v>
+        <v>52.75</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>51.24</v>
+        <v>105.5</v>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
@@ -3840,7 +3837,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>BIB Côtes de Provence Rosé 10L</t>
+          <t>BIB Côtes du Rhône Rouge 10L</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -3854,13 +3851,13 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>52.75</v>
+        <v>31.3</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>105.5</v>
+        <v>31.3</v>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
@@ -3871,12 +3868,12 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>BIB Côtes du Rhône Rouge 10L</t>
+          <t>Ravelin 75cl</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>10 l</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3885,13 +3882,13 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>31.3</v>
+        <v>2.97</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>31.3</v>
+        <v>26.73</v>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
@@ -3902,7 +3899,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ravelin 75cl</t>
+          <t>Gewurztraminer 75cl</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -3916,13 +3913,13 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>2.97</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>26.73</v>
+        <v>99.7</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -3933,7 +3930,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Gewurztraminer 75cl</t>
+          <t>Saint Joseph Rouge 75cl</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -3947,13 +3944,13 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>9.970000000000001</v>
+        <v>12.96</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>99.7</v>
+        <v>116.64</v>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
@@ -3964,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge 75cl</t>
+          <t>Moulin à Vent 75cl</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -3978,13 +3975,13 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>12.96</v>
+        <v>10.88</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>116.64</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
@@ -3995,7 +3992,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Moulin à Vent 75cl</t>
+          <t>Haute Côte de Beaune 75cl</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -4009,13 +4006,13 @@
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>10.88</v>
+        <v>14.24</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>87.04000000000001</v>
+        <v>85.44</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
@@ -4026,7 +4023,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Haute Côte de Beaune 75cl</t>
+          <t>Chablis 75cl</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -4040,13 +4037,13 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>14.24</v>
+        <v>13.37</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>85.44</v>
+        <v>93.59</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
@@ -4057,7 +4054,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Chablis 75cl</t>
+          <t>Saint Véran 75cl</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -4071,13 +4068,13 @@
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>13.37</v>
+        <v>17.46</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>93.59</v>
+        <v>436.5</v>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
@@ -4088,7 +4085,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Saint Véran 75cl</t>
+          <t>Bordeaux Supérieur 75cl</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -4102,13 +4099,13 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>17.46</v>
+        <v>6.28</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>436.5</v>
+        <v>6.28</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
@@ -4119,7 +4116,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Bordeaux Supérieur 75cl</t>
+          <t>Grand Pavois 75cl</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4133,13 +4130,13 @@
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>6.28</v>
+        <v>5.23</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -4150,7 +4147,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Grand Pavois 75cl</t>
+          <t>Arbois Trousseau 75cl</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -4164,24 +4161,24 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>5.23</v>
+        <v>9.77</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Arbois Trousseau 75cl</t>
+          <t>Arbois Béthanie 75cl</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -4195,13 +4192,13 @@
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>9.77</v>
+        <v>10.31</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>97.7</v>
+        <v>144.34</v>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
@@ -4212,12 +4209,12 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Arbois Béthanie 75cl</t>
+          <t>Vin de Paille 37,5cl</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>37,5 cl</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -4226,13 +4223,13 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>10.31</v>
+        <v>16.61</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>144.34</v>
+        <v>33.22</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
@@ -4243,12 +4240,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Vin de Paille 37,5cl</t>
+          <t>Arbois Savagnin 75cl</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>37,5 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4257,13 +4254,13 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>16.61</v>
+        <v>11.85</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>33.22</v>
+        <v>94.8</v>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
@@ -4274,12 +4271,12 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Arbois Savagnin 75cl</t>
+          <t>Arbois Béthanie 37,5cl</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>37,5 cl</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -4288,13 +4285,13 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>11.85</v>
+        <v>6.68</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>94.8</v>
+        <v>106.88</v>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
@@ -4305,12 +4302,12 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Arbois Béthanie 37,5cl</t>
+          <t>Arbois Chardonnay 75cl</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>37,5 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4319,13 +4316,13 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>6.68</v>
+        <v>7.27</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>106.88</v>
+        <v>130.86</v>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
@@ -4336,12 +4333,12 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay 75cl</t>
+          <t>Arbois Vin Jaune 62cl</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>62 cl</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -4350,13 +4347,13 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>7.27</v>
+        <v>19.13</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>130.86</v>
+        <v>76.52</v>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
@@ -4367,12 +4364,12 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune 62cl</t>
+          <t>L'Esprit Grassier Rosé 75cl</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>62 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -4381,13 +4378,13 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>19.13</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>76.52</v>
+        <v>0</v>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
@@ -4398,7 +4395,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>L'Esprit Grassier Rosé 75cl</t>
+          <t>Bohème Rosé (Le Pive) 75cl</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -4412,13 +4409,13 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>8.460000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
@@ -4429,7 +4426,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Bohème Rosé (Le Pive) 75cl</t>
+          <t>Rosé Les Jamelles 75cl</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -4443,13 +4440,13 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>8.279999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>82.8</v>
+        <v>39.92</v>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
@@ -4460,7 +4457,7 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles 75cl</t>
+          <t>Champagne Ruinart 75cl</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -4474,13 +4471,13 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>4.99</v>
+        <v>44.63</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>39.92</v>
+        <v>0</v>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
@@ -4491,7 +4488,7 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Champagne Ruinart 75cl</t>
+          <t>Champagne Jean Sandrin 75cl</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -4505,13 +4502,13 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>44.63</v>
+        <v>16.55</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0</v>
+        <v>132.4</v>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
@@ -4522,7 +4519,7 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Champagne Jean Sandrin 75cl</t>
+          <t>Crémant du Jura 75cl</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -4539,10 +4536,10 @@
         <v>8</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>16.55</v>
+        <v>7.75</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>132.4</v>
+        <v>62</v>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
@@ -4553,7 +4550,7 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Crémant du Jura 75cl</t>
+          <t>Macvin 75cl</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -4567,13 +4564,13 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7.75</v>
+        <v>13.67</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>62</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
@@ -4584,12 +4581,12 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Macvin 75cl</t>
+          <t>Grand Marnier 70cl</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -4598,13 +4595,13 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>13.67</v>
+        <v>21.08</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>68.34999999999999</v>
+        <v>42.16</v>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
@@ -4615,7 +4612,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Grand Marnier 70cl</t>
+          <t>Crème de Cassis 70cl</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -4632,10 +4629,10 @@
         <v>2</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>21.08</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>42.16</v>
+        <v>17.42</v>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
@@ -4646,7 +4643,7 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Crème de Cassis 70cl</t>
+          <t>Liqueur de Poire 70cl</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -4660,13 +4657,13 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>8.710000000000001</v>
+        <v>16.43</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>17.42</v>
+        <v>16.43</v>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
@@ -4677,7 +4674,7 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Liqueur de Poire 70cl</t>
+          <t>Liqueur de Sapin 70cl</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -4691,13 +4688,13 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>16.43</v>
+        <v>18.91</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>16.43</v>
+        <v>37.82</v>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
@@ -4706,50 +4703,19 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Liqueur de Sapin 70cl</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>70 cl</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Alcools et vins</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="7" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>37.82</v>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>TOTAL 2022-2023</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr"/>
-      <c r="C103" s="12" t="inlineStr"/>
-      <c r="D103" s="12" t="inlineStr"/>
-      <c r="E103" s="12" t="inlineStr"/>
-      <c r="F103" s="13" t="n">
-        <v>3674.17</v>
-      </c>
-      <c r="G103" s="12" t="inlineStr"/>
+      <c r="B102" s="10" t="inlineStr"/>
+      <c r="C102" s="10" t="inlineStr"/>
+      <c r="D102" s="10" t="inlineStr"/>
+      <c r="E102" s="10" t="inlineStr"/>
+      <c r="F102" s="11" t="n">
+        <v>3647.96</v>
+      </c>
+      <c r="G102" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7574,19 +7540,19 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>TOTAL 2023-2024</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr"/>
-      <c r="C92" s="12" t="inlineStr"/>
-      <c r="D92" s="12" t="inlineStr"/>
-      <c r="E92" s="12" t="inlineStr"/>
-      <c r="F92" s="13" t="n">
+      <c r="B92" s="10" t="inlineStr"/>
+      <c r="C92" s="10" t="inlineStr"/>
+      <c r="D92" s="10" t="inlineStr"/>
+      <c r="E92" s="10" t="inlineStr"/>
+      <c r="F92" s="11" t="n">
         <v>4536.41</v>
       </c>
-      <c r="G92" s="12" t="inlineStr"/>
+      <c r="G92" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10163,19 +10129,19 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>TOTAL 2024-2025</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr"/>
-      <c r="C84" s="12" t="inlineStr"/>
-      <c r="D84" s="12" t="inlineStr"/>
-      <c r="E84" s="12" t="inlineStr"/>
-      <c r="F84" s="13" t="n">
+      <c r="B84" s="10" t="inlineStr"/>
+      <c r="C84" s="10" t="inlineStr"/>
+      <c r="D84" s="10" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr"/>
+      <c r="F84" s="11" t="n">
         <v>4533.22</v>
       </c>
-      <c r="G84" s="12" t="inlineStr"/>
+      <c r="G84" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10279,16 +10245,16 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>63</v>
@@ -10297,13 +10263,13 @@
         <v>63</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>617.91</v>
+        <v>597.67</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>3056.26</v>
+        <v>3050.29</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>3674.17</v>
+        <v>3647.96</v>
       </c>
       <c r="L2" s="7" t="n"/>
     </row>
@@ -10346,7 +10312,7 @@
         <v>4536.41</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>862.24</v>
+        <v>888.45</v>
       </c>
     </row>
     <row r="4">
@@ -10458,109 +10424,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>2023-03-31</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>INVENTAIRE H.T. DEMI LUNE 31/03/2023</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="13" t="n">
         <v>727.7</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="13" t="n">
         <v>3050.29</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="13" t="n">
         <v>3777.99</v>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>ALIMENTAIRE (frais, surgeles, epicerie) : 1734.15 ; CREMERIE : 158.85 ; VIANDE-CHARCUTERIE : 255.63 ; PRODUITS D'ENTRETIEN ET DIVERS : 1103.99</t>
         </is>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="13" t="n">
         <v>7030.61</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Inventaire_Demi_Lune_2023-03-31.pdf, p. 1 (tableau dactylographie, date)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>2024-03-31</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>INVENTAIRE H.T. AU 31 MARS 2024</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="13" t="n">
         <v>870.59</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="13" t="n">
         <v>3937.07</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="13" t="n">
         <v>4807.66</v>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Produits d'entretien et Divers : 1000.30 ; Alimentation : 4065.17</t>
         </is>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="13" t="n">
         <v>9873.07</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>Inventaire_Demi_Lune_2024-03-31.pdf, p. 1 (page dactylographiee, datee) ; report manuscrit des memes totaux en p. 7</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>INVENTAIRE HT 31/03/2025</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="13" t="n">
         <v>765.74</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="13" t="n">
         <v>3768.51</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="13" t="n">
         <v>4534.25</v>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>ALIMENTATION (frais, surgeles, epicerie) : 3654.92 ; DIVERS NON COMESTIBLES : 1585.00</t>
         </is>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="13" t="n">
         <v>9774.17</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Inventaire_Demi_Lune_2025-03-31.pdf, p. 1 (page dactylographiee, datee)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Rapprochement avec la variation de stock boissons retenue par le service (compte 310200), sous la convention comptable variation = stock initial moins stock final.</t>
         </is>
@@ -10664,7 +10630,7 @@
       <c r="E11" s="7" t="n">
         <v>-273.41</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="15" t="n">
         <v>546.8200000000001</v>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -10681,7 +10647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10707,62 +10673,107 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Erreurs de frappe rectifiees (cloture 31/03/2023)</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Clan Campbell 70cl : 17.56 saisi au lieu de 12.56 ; Creme de Mure 100cl : 8.22 saisi au lieu de 8.27 ; Creme de Cerise 100cl : 16.78 saisi au lieu de 15.76</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="n">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Erreurs de frappe rectifiees, page 11 du PDF 2023 (alcools et vins)</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Clan Campbell 70cl : 17.56 saisi au lieu de 12.56 ; Creme de Mure 100cl : 8.22 saisi au lieu de 8.27 ; Creme de Cerise 100cl : 16.78 saisi au lieu de 15.76. Le CSV publie porte desormais les valeurs de l'etat d'origine.</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
         <v>-5.97</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Erreurs de frappe rectifiees, page 10 du PDF 2023 (boissons sans alcool)</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Vittel 50cl : ligne inexistante sur l'etat d'origine, doublon de la ligne San Pellegrino 50cl (33 unites a 0,88 EUR, 29,04 EUR) : supprimee ; Infusion verveine : 1 unite a 8,80 EUR portee sur l'etat d'origine, transcrite a 0 : retablie ; Orangina 33cl : 33 unites a 0,59 EUR sur l'etat d'origine, transcrites 13 a 1,59 EUR : quantite et prix unitaire retablis, valeur inchangee (19,47 EUR) ; Peppermint infusion : prix unitaire 3,44 EUR sur l'etat d'origine, transcrit 6,42 EUR ; quantite nulle, valeur inchangee (0 EUR). Le CSV publie porte desormais les valeurs de l'etat d'origine.</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>-20.24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Total alcools et vins au 31/03/2023, apres rectification</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>3 056,26 EUR transcrits, 3 050,29 EUR portes sur l'etat d'origine (page 11 du PDF 2023, reproduite par le service p. 33 de sa reponse). C'est l'etat d'origine qui fait foi.</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="n">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Transcription rectifiee : 3050.29 EUR, soit exactement le total porte en pied de la page 11 du PDF 2023, page que le service reproduit lui-meme p. 33 de sa reponse. La transcription anterieure indiquait 3 056,26 EUR. C'est l'etat d'origine qui fait foi.</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
         <v>3050.29</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Total boissons sans alcool au 31/03/2023, apres rectification</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Transcription rectifiee des boissons : 597.67 EUR. La page 10 du PDF porte en outre sucre morceaux (0.00 EUR), petites galettes st michel (70.12 EUR), petites madeleines st michel (36.76 EUR), mix crackers (23.15 EUR), soit 130.03 EUR d'alimentation hors perimetre du CSV. La somme des deux, 727.70 EUR, est exactement le total imprime au bas de la page 10.</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>727.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Colonne de fiabilite de la transcription</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>27 lignes sur 273 sont marquees « a verifier » dans les CSV publies (1 929,34 EUR), dont trois lignes de reconciliation au 31/03/2025 qui ne designent aucun produit (413,00 EUR). Ces reserves portent sur la TRANSCRIPTION, pas sur les etats d'origine, dont les totaux dates figurent dans la feuille precedente.</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>27 lignes sur 272 sont marquees « a verifier » dans les CSV publies (1929.34 EUR). Ces reserves portent sur la TRANSCRIPTION, pas sur les etats d'origine, dont les totaux dates figurent dans la feuille precedente.</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>1929.34</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Lignes de reconciliation du 31/03/2025, non identifiees</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>3 des lignes ci-dessus, toutes au 31/03/2025, ne designent aucun produit : ce sont des reliquats de valeur (413.00 EUR, dont 318.41 EUR en alcools et vins) qui ferment la transcription sur les totaux dates de l'etat d'origine. Consequence a enoncer clairement : tant que ces lignes ne sont pas rattachees a un article, le stock d'alcools exprime EN LITRES au 31/03/2025 qui se deduit du CSV est un MINORANT. Les bouteilles correspondant a ces 318,41 EUR existent et sont comprises dans le total date de l'etat, mais leur contenance ne peut pas etre imputee faute de libelle. Toute reconstitution de volumes appuyee sur ce stock joue donc contre le contribuable, jamais en sa faveur.</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Perimetre du CSV</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Les CSV retiennent les seules boissons : ils excluent les biscuits, le sucre, les pailles et les consommables inscrits sur les memes pages d'inventaire. Leurs totaux ne sont donc pas comparables aux totaux des pages recapitulatives.</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n"/>
+      <c r="C8" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
